--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-05T08:47:41+00:00</t>
+    <t>2025-07-06T14:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-06T14:27:51+00:00</t>
+    <t>2025-07-06T14:40:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-06T14:40:53+00:00</t>
+    <t>2025-07-06T14:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-06T14:44:44+00:00</t>
+    <t>2025-07-06T14:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-06T14:51:44+00:00</t>
+    <t>2025-07-06T16:51:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-06T16:51:24+00:00</t>
+    <t>2025-07-07T15:12:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:12:09+00:00</t>
+    <t>2025-07-07T15:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:41:30+00:00</t>
+    <t>2025-07-07T16:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-refacto-errors/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T16:21:37+00:00</t>
+    <t>2025-07-08T07:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
